--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,51 +2462,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135410045</v>
+        <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93366</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720191</v>
+        <v>720131</v>
       </c>
       <c r="R18" t="n">
-        <v>7334923</v>
+        <v>7334863</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,22 +2531,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,34 +2560,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135410045</t>
+          <t>https://artportalen.se/Sighting/136858066</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134434127</v>
+        <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93283</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2589,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2617,13 +2622,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720229</v>
+        <v>720163</v>
       </c>
       <c r="R19" t="n">
-        <v>7334876</v>
+        <v>7334943</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2647,12 +2652,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2683,16 +2698,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134434127</t>
+          <t>https://artportalen.se/Sighting/136858068</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135403995</v>
+        <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2700,37 +2715,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720190</v>
+        <v>720230</v>
       </c>
       <c r="R20" t="n">
-        <v>7334890</v>
+        <v>7334887</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2754,22 +2773,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,65 +2808,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135403995</t>
+          <t>https://artportalen.se/Sighting/136858069</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135403866</v>
+        <v>135410045</v>
       </c>
       <c r="B21" t="n">
-        <v>80062</v>
+        <v>93366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720202</v>
+        <v>720191</v>
       </c>
       <c r="R21" t="n">
-        <v>7334913</v>
+        <v>7334923</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2881,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,33 +2917,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135403866</t>
+          <t>https://artportalen.se/Sighting/135410045</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135403991</v>
+        <v>134434127</v>
       </c>
       <c r="B22" t="n">
-        <v>80062</v>
+        <v>93283</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,37 +2952,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720134</v>
+        <v>720229</v>
       </c>
       <c r="R22" t="n">
-        <v>7334845</v>
+        <v>7334876</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,22 +3010,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,27 +3035,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135403991</t>
+          <t>https://artportalen.se/Sighting/134434127</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135403994</v>
+        <v>135403995</v>
       </c>
       <c r="B23" t="n">
-        <v>80062</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,21 +3063,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3060,13 +3087,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720191</v>
+        <v>720190</v>
       </c>
       <c r="R23" t="n">
-        <v>7334871</v>
+        <v>7334890</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3095,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3105,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,13 +3158,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135403994</t>
+          <t>https://artportalen.se/Sighting/135403995</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135408005</v>
+        <v>135403866</v>
       </c>
       <c r="B24" t="n">
         <v>80062</v>
@@ -3168,14 +3195,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720212</v>
+        <v>720202</v>
       </c>
       <c r="R24" t="n">
-        <v>7334885</v>
+        <v>7334913</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3207,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3217,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,24 +3259,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135408005</t>
+          <t>https://artportalen.se/Sighting/135403866</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135410050</v>
+        <v>135403991</v>
       </c>
       <c r="B25" t="n">
         <v>80062</v>
@@ -3280,17 +3307,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720236</v>
+        <v>720134</v>
       </c>
       <c r="R25" t="n">
-        <v>7334843</v>
+        <v>7334845</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,27 +3371,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135410050</t>
+          <t>https://artportalen.se/Sighting/135403991</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135403666</v>
+        <v>135403994</v>
       </c>
       <c r="B26" t="n">
-        <v>58086</v>
+        <v>80062</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,21 +3399,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3396,13 +3423,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720143</v>
+        <v>720191</v>
       </c>
       <c r="R26" t="n">
-        <v>7334844</v>
+        <v>7334871</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3456,27 +3483,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135403666</t>
+          <t>https://artportalen.se/Sighting/135403994</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135404003</v>
+        <v>135408005</v>
       </c>
       <c r="B27" t="n">
-        <v>79466</v>
+        <v>80062</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,37 +3511,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>260591</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720213</v>
+        <v>720212</v>
       </c>
       <c r="R27" t="n">
-        <v>7334858</v>
+        <v>7334885</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3543,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3553,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,27 +3595,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135404003</t>
+          <t>https://artportalen.se/Sighting/135408005</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135408004</v>
+        <v>135410050</v>
       </c>
       <c r="B28" t="n">
-        <v>79466</v>
+        <v>80062</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,37 +3623,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>260591</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720220</v>
+        <v>720236</v>
       </c>
       <c r="R28" t="n">
-        <v>7334868</v>
+        <v>7334843</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3665,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,27 +3707,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135408004</t>
+          <t>https://artportalen.se/Sighting/135410050</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135408006</v>
+        <v>135403666</v>
       </c>
       <c r="B29" t="n">
-        <v>79466</v>
+        <v>58086</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,37 +3735,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>260591</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720217</v>
+        <v>720143</v>
       </c>
       <c r="R29" t="n">
-        <v>7334878</v>
+        <v>7334844</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3767,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3777,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,27 +3819,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135408006</t>
+          <t>https://artportalen.se/Sighting/135403666</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135504169</v>
+        <v>135404003</v>
       </c>
       <c r="B30" t="n">
-        <v>79467</v>
+        <v>79466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,13 +3871,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720182</v>
+        <v>720213</v>
       </c>
       <c r="R30" t="n">
-        <v>7334898</v>
+        <v>7334858</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3889,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,63 +3931,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135504169</t>
+          <t>https://artportalen.se/Sighting/135404003</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135410046</v>
+        <v>135408004</v>
       </c>
       <c r="B31" t="n">
-        <v>80337</v>
+        <v>79466</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720205</v>
+        <v>720220</v>
       </c>
       <c r="R31" t="n">
-        <v>7334872</v>
+        <v>7334868</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3989,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3999,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4008,23 +4037,357 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408004</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135408006</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79466</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720217</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7334878</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408006</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135504169</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720182</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7334898</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504169</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135410046</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80337</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720205</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7334872</v>
+      </c>
+      <c r="S34" t="n">
+        <v>12</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135410046</t>
         </is>
@@ -4062,6 +4425,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -2465,7 +2465,7 @@
         <v>136858066</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136858068</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>136858069</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
